--- a/output/HS_Code_Summary_ABO_Valve_260600091.xlsx
+++ b/output/HS_Code_Summary_ABO_Valve_260600091.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dokumenty a poznámky" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -647,7 +647,7 @@
       </c>
       <c r="H2" s="6">
         <f>F2*G2</f>
-        <v/>
+        <v>143.582</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>173.632</v>
@@ -657,7 +657,7 @@
       </c>
       <c r="K2" s="7">
         <f>F2*J2</f>
-        <v/>
+        <v>2513.382</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -687,21 +687,21 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="11">
         <f>SUM(F2:F2)</f>
-        <v/>
+        <v>1394</v>
       </c>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="12">
         <f>SUM(H2:H2)</f>
-        <v/>
+        <v>143.582</v>
       </c>
       <c r="I3" s="12">
         <f>SUM(I2:I2)</f>
-        <v/>
+        <v>173.632</v>
       </c>
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="13">
         <f>SUM(K2:K2)</f>
-        <v/>
+        <v>2513.382</v>
       </c>
       <c r="L3" s="10" t="n"/>
       <c r="M3" s="10" t="n"/>
